--- a/Interoperability API Metrics Example ORW.xlsx
+++ b/Interoperability API Metrics Example ORW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pkroft/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6BEF2EA-96F8-8045-921C-9B9FEA360B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF48A8F4-D60E-5942-95F8-715199AE5F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" tabRatio="804" firstSheet="1" activeTab="2" xr2:uid="{8B66A70A-2856-4B2F-BE26-37F5B97C85EB}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" tabRatio="804" activeTab="1" xr2:uid="{8B66A70A-2856-4B2F-BE26-37F5B97C85EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CMS Attestations'!$A$2:$F$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metric Data'!$A$2:$J$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metric Data'!$A$2:$J$408</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Metric Definitions'!$A$2:$M$12</definedName>
     <definedName name="Metric_ID">'Metric Definitions'!$E$3:$E$5000</definedName>
     <definedName name="MetricsList">InputValues!#REF!</definedName>
@@ -142,12 +142,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="565">
   <si>
     <t>Welcome to the Operational Report Workbook (ORW) for MES Metrics</t>
   </si>
   <si>
-    <t>Version 3.01</t>
+    <t>Version 3.02</t>
   </si>
   <si>
     <t>Introduction</t>
@@ -1095,6 +1095,9 @@
   </si>
   <si>
     <t>Interoperability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example - TN Interop APIs </t>
   </si>
   <si>
     <t>Yes</t>
@@ -2368,16 +2371,16 @@
     <t>Note</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>IO01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TN-CR-IO-01.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usage of Patient Access API </t>
+    <t>IOPAA</t>
+  </si>
+  <si>
+    <t>IOPAA01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN-CR-IOPAA-01.1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of Patient Access API </t>
   </si>
   <si>
     <t xml:space="preserve">The total number of unique beneficiaries whose data are transferred via the Patient Access API to a health app designated by the beneficiary </t>
@@ -2395,22 +2398,22 @@
     <t>This is regulation required metric for Patient Access API.</t>
   </si>
   <si>
-    <t>TN-CR-IO-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usage of Patient Access API More Than Once </t>
+    <t>TN-CR-IOPAA-01.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of Patient Access API More Than Once </t>
   </si>
   <si>
     <t xml:space="preserve">The total number of unique beneficiaries whose data are transferred more than once via the Patient Access API to a health app designated by the beneficiary </t>
   </si>
   <si>
-    <t>STIO01</t>
+    <t>STIOPAA01</t>
   </si>
   <si>
     <t>Example - Increase the number of new users for Patient Access API</t>
   </si>
   <si>
-    <t>TN-ST-IO-01.1</t>
+    <t>TN-ST-IOPAA-01.1</t>
   </si>
   <si>
     <t>Example - First Time Use of Patient Access API</t>
@@ -2422,13 +2425,34 @@
     <t>Example - This complements the regulation required metric for Patient Access API and measure progress made in increasing usage of the API.</t>
   </si>
   <si>
-    <t>STIO02</t>
+    <t>STIOPAA02</t>
+  </si>
+  <si>
+    <t>Example - Increase number of registered third-party developers</t>
+  </si>
+  <si>
+    <t>TN-ST-IOPAA-02.1</t>
+  </si>
+  <si>
+    <t>Example - Number of registered third-party developers</t>
+  </si>
+  <si>
+    <t>Example - The number of unique third-party devlopers that are registered to develop apps with Patient Access API</t>
+  </si>
+  <si>
+    <t>Quarterly</t>
+  </si>
+  <si>
+    <t>IOPRD</t>
+  </si>
+  <si>
+    <t>STIOPRD01</t>
   </si>
   <si>
     <t>Example - Ensure the completeness of Provider Directory API</t>
   </si>
   <si>
-    <t xml:space="preserve">TN-ST-IO-02.1 </t>
+    <t xml:space="preserve">TN-ST-IOPRD-01.1 </t>
   </si>
   <si>
     <t>Example - Number of Active Providers Loaded</t>
@@ -2437,10 +2461,13 @@
     <t>Example - Total number of active providers loaded via the Provider Directory API.</t>
   </si>
   <si>
+    <t>STIOPRD02</t>
+  </si>
+  <si>
     <t>Example - Expand the use of Provider Directory API</t>
   </si>
   <si>
-    <t>TN-ST-IO-02.2</t>
+    <t>TN-ST-IOPRD-02.1</t>
   </si>
   <si>
     <t>Example - Number of Provider Directory API Queries</t>
@@ -2449,16 +2476,101 @@
     <t xml:space="preserve">Example - The total number of actual queries requested of the API, with a breakdown by provider categories of Primary Care Physicians and Specialist.  </t>
   </si>
   <si>
+    <t>STIOPRD03</t>
+  </si>
+  <si>
     <t>Example - Maintain an accurate Provider Directory</t>
   </si>
   <si>
-    <t>TN-ST-IO-02.3</t>
-  </si>
-  <si>
-    <t>Example - Number of providers updates applied in the Provider Directory</t>
+    <t>TN-ST-IOPRD-03.1</t>
+  </si>
+  <si>
+    <t>Example - Number of Providers Updates Applied in the Provider Directory</t>
   </si>
   <si>
     <t>Exampe - Total number of updates appied in the Provider Directory</t>
+  </si>
+  <si>
+    <t>IOPRA</t>
+  </si>
+  <si>
+    <t>STIOPRA01</t>
+  </si>
+  <si>
+    <t>Example - Receive Prior Authorization Requests</t>
+  </si>
+  <si>
+    <t>TN-ST-IOPRA-01.1</t>
+  </si>
+  <si>
+    <t>Example - Number of Prior Authorization Requests Received</t>
+  </si>
+  <si>
+    <t>Example - Total number of Prior Authorization requests received</t>
+  </si>
+  <si>
+    <t>STIOPRA02</t>
+  </si>
+  <si>
+    <t>Example - Process Prior Authorization Requests</t>
+  </si>
+  <si>
+    <t>TN-ST-IOPRA-02.1</t>
+  </si>
+  <si>
+    <t>Example - Number of Prior Authorization Requests Processed</t>
+  </si>
+  <si>
+    <t>Example - Total number of Prior Authorization requests processed</t>
+  </si>
+  <si>
+    <t>IOPTP</t>
+  </si>
+  <si>
+    <t>STIOPTP01</t>
+  </si>
+  <si>
+    <t>Exampe - Process Payer-to Payer Requests</t>
+  </si>
+  <si>
+    <t>TN-ST-IOPTP-01.1</t>
+  </si>
+  <si>
+    <t>Exampe - Number of Payer-to Payer Requests Processed</t>
+  </si>
+  <si>
+    <t>Example - Total number of Pay-to-Payer requests processed</t>
+  </si>
+  <si>
+    <t>IOPAC</t>
+  </si>
+  <si>
+    <t>STIOPAC01</t>
+  </si>
+  <si>
+    <t>Exampe - Process Provider Access Requests</t>
+  </si>
+  <si>
+    <t>TN-ST-IOPAC-01.1</t>
+  </si>
+  <si>
+    <t>Exampe - Number of Provider Access Requests Processed</t>
+  </si>
+  <si>
+    <t>Example - Total number of Provider Access requests processed</t>
+  </si>
+  <si>
+    <t>CEF09|CEF12|CEF18</t>
+  </si>
+  <si>
+    <t>TN-CR-IOPAA-CEF-09.1</t>
+  </si>
+  <si>
+    <t>Open privacy and security risks</t>
+  </si>
+  <si>
+    <t>Sourced from the POA&amp;M(s), and reported quarterly in [list the months it will be reported in by the state here] on the Metric Values tab (using three measure counts). 
+Must include all technical environments hosting the system being reported on.</t>
   </si>
   <si>
     <r>
@@ -2782,46 +2894,49 @@
     <t>Medicaid</t>
   </si>
   <si>
-    <t>200 as the current monthly benchmark.</t>
+    <t>Example - State will monitor this metric and determine a proper benchmark</t>
+  </si>
+  <si>
+    <t>Example - Number of beneficiaries who data is transferred more than once</t>
+  </si>
+  <si>
+    <t>Example - Number of first time users of Patient Access API</t>
+  </si>
+  <si>
+    <t>Example - Number of active providers loaded</t>
+  </si>
+  <si>
+    <t>Example - No benchmark is set since this metric depends on what additions are needed.</t>
+  </si>
+  <si>
+    <t>Example - Queries of Provider Directory for Primary Care physicians</t>
+  </si>
+  <si>
+    <t>Example - Queries of Provider Directory for Specialists</t>
+  </si>
+  <si>
+    <t>Example - Number of provider updates</t>
+  </si>
+  <si>
+    <t>Example - No benchmark is set since this metric depends on what updates are needed.</t>
   </si>
   <si>
     <t>Example - API is newly put into place, and state expects increased usage over time.</t>
   </si>
   <si>
-    <t>Example - Number of beneficiaries who data is transferred more than once</t>
-  </si>
-  <si>
-    <t>Example - State will monitor this metric and determine a proper benchmark</t>
-  </si>
-  <si>
-    <t>Example - Number of first time users of Patient Access API</t>
-  </si>
-  <si>
-    <t>20 as the current monthly benchmark.</t>
-  </si>
-  <si>
-    <t>Example - Number of active providers loaded</t>
-  </si>
-  <si>
-    <t>Example - No benchmark is set since this metric depends on what additions are needed.</t>
-  </si>
-  <si>
-    <t>Example - Queries of Provider Directory for Primary Care physicians</t>
-  </si>
-  <si>
-    <t>300 as the current monthly benchmark</t>
-  </si>
-  <si>
-    <t>Example - Queries of Provider Directory for Specialists</t>
-  </si>
-  <si>
-    <t>200 as the current monthly benchmark</t>
-  </si>
-  <si>
-    <t>Example - Number of provider updates</t>
-  </si>
-  <si>
-    <t>Example - No benchmark is set since this metric depends on what updates are needed.</t>
+    <t>Exampe - Number of Provider Access Processed</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Include all issues from all technical environments hosting APIs</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Any Severity</t>
   </si>
   <si>
     <t>Metric Types</t>
@@ -2848,9 +2963,6 @@
     <t>Metrics</t>
   </si>
   <si>
-    <t>Quarterly</t>
-  </si>
-  <si>
     <t>DSSDW</t>
   </si>
   <si>
@@ -2905,7 +3017,22 @@
     <t>Ended</t>
   </si>
   <si>
+    <t>Interoperability Patient Access API</t>
+  </si>
+  <si>
     <t>If the metrics ID column location changes, this formula must be updated in the name manager.</t>
+  </si>
+  <si>
+    <t>Interoperability Provider Directory API</t>
+  </si>
+  <si>
+    <t>Interoperability Prior Authorization API</t>
+  </si>
+  <si>
+    <t>Interoperability Payer-to-Payer API</t>
+  </si>
+  <si>
+    <t>Interoperability Provider Access API</t>
   </si>
   <si>
     <t>LTSS</t>
@@ -3103,7 +3230,9 @@
     <t>Not seeing ALL of the dropdowns: Three things to check for debugging: a) Check the name manager ranges. B) Check the formulas in cols AC, AD, and AE. C) The target columns or length of MetricDataDrop list in the name manager.</t>
   </si>
   <si>
-    <t xml:space="preserve">Example - TN Interop APIs </t>
+    <t xml:space="preserve">Note that if the state has mutliple systems for APIs, the state needs to combine the findings from all these systems. 
+Note also that for reporting this CEF metric, use IOPAA as a the Module label.
+</t>
   </si>
 </sst>
 </file>
@@ -3781,7 +3910,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4121,6 +4250,10 @@
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4763,10 +4896,10 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="132" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="108"/>
+      <c r="C10" s="109"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -4775,7 +4908,7 @@
       <c r="E11" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jV0d67msBpEpathDAk9B9QrUpNfY3J0k4AnSqHqr8EMQ+GDU6ghKwtsysAAt/gZU2COWsOWKR1rk2VhVudLAOg==" saltValue="bMU33xCjdjz3AJ5HMUIz9g==" spinCount="100000" sheet="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="z17NIGrJLGgIXD3wLcx8nD3FyvNEflCevE9nBkMUgXxAURJjlKzb/z0w36mOldtoE4Z6W3uLnjEIVkJBCm8i1g==" saltValue="S6xWVTNNFD8ymhlX07AZ5A==" spinCount="100000" sheet="1" sort="0" autoFilter="0"/>
   <mergeCells count="1">
     <mergeCell ref="B10:C10"/>
   </mergeCells>
@@ -7666,7 +7799,7 @@
         <v>195</v>
       </c>
       <c r="B215" s="47" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C215" s="92" t="s">
         <v>41</v>
@@ -7675,7 +7808,7 @@
         <v>42</v>
       </c>
       <c r="E215" s="94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F215" s="95"/>
     </row>
@@ -7684,7 +7817,7 @@
         <v>195</v>
       </c>
       <c r="B216" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C216" s="70" t="s">
         <v>43</v>
@@ -7693,7 +7826,7 @@
         <v>44</v>
       </c>
       <c r="E216" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F216" s="98"/>
     </row>
@@ -7702,7 +7835,7 @@
         <v>195</v>
       </c>
       <c r="B217" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C217" s="70" t="s">
         <v>45</v>
@@ -7711,7 +7844,7 @@
         <v>46</v>
       </c>
       <c r="E217" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F217" s="98"/>
     </row>
@@ -7720,7 +7853,7 @@
         <v>195</v>
       </c>
       <c r="B218" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C218" s="70" t="s">
         <v>47</v>
@@ -7729,10 +7862,10 @@
         <v>48</v>
       </c>
       <c r="E218" s="58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F218" s="99" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -7740,7 +7873,7 @@
         <v>195</v>
       </c>
       <c r="B219" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C219" s="70" t="s">
         <v>49</v>
@@ -7749,7 +7882,7 @@
         <v>50</v>
       </c>
       <c r="E219" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F219" s="98"/>
     </row>
@@ -7758,7 +7891,7 @@
         <v>195</v>
       </c>
       <c r="B220" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C220" s="70" t="s">
         <v>51</v>
@@ -7767,7 +7900,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F220" s="98"/>
     </row>
@@ -7776,7 +7909,7 @@
         <v>195</v>
       </c>
       <c r="B221" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C221" s="70" t="s">
         <v>53</v>
@@ -7785,7 +7918,7 @@
         <v>54</v>
       </c>
       <c r="E221" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F221" s="98"/>
     </row>
@@ -7794,7 +7927,7 @@
         <v>195</v>
       </c>
       <c r="B222" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C222" s="70" t="s">
         <v>55</v>
@@ -7803,7 +7936,7 @@
         <v>56</v>
       </c>
       <c r="E222" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F222" s="98"/>
     </row>
@@ -7812,7 +7945,7 @@
         <v>195</v>
       </c>
       <c r="B223" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C223" s="70" t="s">
         <v>57</v>
@@ -7821,7 +7954,7 @@
         <v>58</v>
       </c>
       <c r="E223" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F223" s="98"/>
     </row>
@@ -7830,7 +7963,7 @@
         <v>195</v>
       </c>
       <c r="B224" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C224" s="70" t="s">
         <v>59</v>
@@ -7839,7 +7972,7 @@
         <v>60</v>
       </c>
       <c r="E224" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F224" s="98"/>
     </row>
@@ -7848,7 +7981,7 @@
         <v>195</v>
       </c>
       <c r="B225" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C225" s="70" t="s">
         <v>61</v>
@@ -7857,7 +7990,7 @@
         <v>62</v>
       </c>
       <c r="E225" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F225" s="98"/>
     </row>
@@ -7866,7 +7999,7 @@
         <v>195</v>
       </c>
       <c r="B226" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C226" s="70" t="s">
         <v>63</v>
@@ -7875,7 +8008,7 @@
         <v>64</v>
       </c>
       <c r="E226" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F226" s="98"/>
     </row>
@@ -7884,7 +8017,7 @@
         <v>195</v>
       </c>
       <c r="B227" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C227" s="70" t="s">
         <v>65</v>
@@ -7893,7 +8026,7 @@
         <v>66</v>
       </c>
       <c r="E227" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F227" s="98"/>
     </row>
@@ -7902,7 +8035,7 @@
         <v>195</v>
       </c>
       <c r="B228" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C228" s="70" t="s">
         <v>67</v>
@@ -7911,7 +8044,7 @@
         <v>68</v>
       </c>
       <c r="E228" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F228" s="98"/>
     </row>
@@ -7920,7 +8053,7 @@
         <v>195</v>
       </c>
       <c r="B229" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C229" s="70" t="s">
         <v>69</v>
@@ -7929,7 +8062,7 @@
         <v>70</v>
       </c>
       <c r="E229" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F229" s="98"/>
     </row>
@@ -7938,7 +8071,7 @@
         <v>195</v>
       </c>
       <c r="B230" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C230" s="70" t="s">
         <v>71</v>
@@ -7947,10 +8080,10 @@
         <v>72</v>
       </c>
       <c r="E230" s="58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F230" s="99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -7958,7 +8091,7 @@
         <v>195</v>
       </c>
       <c r="B231" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C231" s="70" t="s">
         <v>73</v>
@@ -7967,10 +8100,10 @@
         <v>74</v>
       </c>
       <c r="E231" s="58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F231" s="99" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -7978,7 +8111,7 @@
         <v>195</v>
       </c>
       <c r="B232" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C232" s="70" t="s">
         <v>75</v>
@@ -7987,7 +8120,7 @@
         <v>76</v>
       </c>
       <c r="E232" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F232" s="98"/>
     </row>
@@ -7996,7 +8129,7 @@
         <v>195</v>
       </c>
       <c r="B233" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C233" s="70" t="s">
         <v>77</v>
@@ -8005,7 +8138,7 @@
         <v>78</v>
       </c>
       <c r="E233" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F233" s="98"/>
     </row>
@@ -8014,7 +8147,7 @@
         <v>195</v>
       </c>
       <c r="B234" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C234" s="70" t="s">
         <v>79</v>
@@ -8023,7 +8156,7 @@
         <v>80</v>
       </c>
       <c r="E234" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F234" s="98"/>
     </row>
@@ -8032,7 +8165,7 @@
         <v>195</v>
       </c>
       <c r="B235" s="97" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C235" s="70" t="s">
         <v>81</v>
@@ -8041,7 +8174,7 @@
         <v>82</v>
       </c>
       <c r="E235" s="58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F235" s="98"/>
     </row>
@@ -8050,7 +8183,7 @@
         <v>195</v>
       </c>
       <c r="B236" s="101" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C236" s="102" t="s">
         <v>83</v>
@@ -8059,167 +8192,167 @@
         <v>84</v>
       </c>
       <c r="E236" s="104" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F236" s="105"/>
     </row>
     <row r="237" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B237" s="45"/>
       <c r="C237" s="67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D237" s="67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E237" s="58"/>
       <c r="F237" s="58"/>
     </row>
     <row r="238" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B238" s="45"/>
       <c r="C238" s="67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D238" s="67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E238" s="58"/>
       <c r="F238" s="58"/>
     </row>
     <row r="239" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B239" s="45"/>
       <c r="C239" s="67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D239" s="67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E239" s="58"/>
       <c r="F239" s="58"/>
     </row>
     <row r="240" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B240" s="45"/>
       <c r="C240" s="67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D240" s="67" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E240" s="58"/>
       <c r="F240" s="58"/>
     </row>
     <row r="241" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B241" s="45"/>
       <c r="C241" s="67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D241" s="67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E241" s="58"/>
       <c r="F241" s="58"/>
     </row>
     <row r="242" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B242" s="45"/>
       <c r="C242" s="67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D242" s="67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E242" s="58"/>
       <c r="F242" s="58"/>
     </row>
     <row r="243" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B243" s="45"/>
       <c r="C243" s="67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D243" s="67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E243" s="58"/>
       <c r="F243" s="58"/>
     </row>
     <row r="244" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B244" s="45"/>
       <c r="C244" s="67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D244" s="67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E244" s="58"/>
       <c r="F244" s="58"/>
     </row>
     <row r="245" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B245" s="45"/>
       <c r="C245" s="67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D245" s="67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E245" s="58"/>
       <c r="F245" s="58"/>
     </row>
     <row r="246" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B246" s="45"/>
       <c r="C246" s="67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D246" s="67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E246" s="58"/>
       <c r="F246" s="58"/>
     </row>
     <row r="247" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B247" s="45"/>
       <c r="C247" s="67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D247" s="67" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E247" s="58"/>
       <c r="F247" s="58"/>
     </row>
     <row r="248" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C248" s="70" t="s">
         <v>41</v>
@@ -8232,7 +8365,7 @@
     </row>
     <row r="249" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C249" s="70" t="s">
         <v>43</v>
@@ -8245,7 +8378,7 @@
     </row>
     <row r="250" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C250" s="70" t="s">
         <v>45</v>
@@ -8258,7 +8391,7 @@
     </row>
     <row r="251" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C251" s="70" t="s">
         <v>47</v>
@@ -8271,7 +8404,7 @@
     </row>
     <row r="252" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C252" s="70" t="s">
         <v>49</v>
@@ -8284,7 +8417,7 @@
     </row>
     <row r="253" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C253" s="70" t="s">
         <v>51</v>
@@ -8297,7 +8430,7 @@
     </row>
     <row r="254" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C254" s="70" t="s">
         <v>53</v>
@@ -8310,7 +8443,7 @@
     </row>
     <row r="255" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C255" s="70" t="s">
         <v>55</v>
@@ -8323,7 +8456,7 @@
     </row>
     <row r="256" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C256" s="70" t="s">
         <v>57</v>
@@ -8336,7 +8469,7 @@
     </row>
     <row r="257" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C257" s="70" t="s">
         <v>59</v>
@@ -8349,7 +8482,7 @@
     </row>
     <row r="258" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C258" s="70" t="s">
         <v>61</v>
@@ -8362,7 +8495,7 @@
     </row>
     <row r="259" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C259" s="70" t="s">
         <v>63</v>
@@ -8375,7 +8508,7 @@
     </row>
     <row r="260" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C260" s="70" t="s">
         <v>65</v>
@@ -8388,7 +8521,7 @@
     </row>
     <row r="261" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C261" s="70" t="s">
         <v>67</v>
@@ -8401,7 +8534,7 @@
     </row>
     <row r="262" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C262" s="70" t="s">
         <v>69</v>
@@ -8414,7 +8547,7 @@
     </row>
     <row r="263" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C263" s="70" t="s">
         <v>71</v>
@@ -8427,7 +8560,7 @@
     </row>
     <row r="264" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C264" s="70" t="s">
         <v>73</v>
@@ -8440,7 +8573,7 @@
     </row>
     <row r="265" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C265" s="70" t="s">
         <v>75</v>
@@ -8453,7 +8586,7 @@
     </row>
     <row r="266" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C266" s="70" t="s">
         <v>77</v>
@@ -8466,7 +8599,7 @@
     </row>
     <row r="267" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C267" s="70" t="s">
         <v>79</v>
@@ -8479,7 +8612,7 @@
     </row>
     <row r="268" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C268" s="70" t="s">
         <v>81</v>
@@ -8492,7 +8625,7 @@
     </row>
     <row r="269" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C269" s="70" t="s">
         <v>83</v>
@@ -8505,161 +8638,161 @@
     </row>
     <row r="270" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B270" s="45"/>
       <c r="C270" s="67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D270" s="67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E270" s="58"/>
       <c r="F270" s="58"/>
     </row>
     <row r="271" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B271" s="45"/>
       <c r="C271" s="67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D271" s="67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E271" s="58"/>
       <c r="F271" s="58"/>
     </row>
     <row r="272" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B272" s="45"/>
       <c r="C272" s="67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D272" s="67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E272" s="58"/>
       <c r="F272" s="58"/>
     </row>
     <row r="273" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B273" s="45"/>
       <c r="C273" s="67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D273" s="67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E273" s="58"/>
       <c r="F273" s="58"/>
     </row>
     <row r="274" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B274" s="45"/>
       <c r="C274" s="67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D274" s="67" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E274" s="58"/>
       <c r="F274" s="58"/>
     </row>
     <row r="275" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B275" s="45"/>
       <c r="C275" s="67" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D275" s="67" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E275" s="58"/>
       <c r="F275" s="58"/>
     </row>
     <row r="276" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B276" s="45"/>
       <c r="C276" s="67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D276" s="67" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E276" s="58"/>
       <c r="F276" s="58"/>
     </row>
     <row r="277" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B277" s="45"/>
       <c r="C277" s="67" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D277" s="72" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E277" s="58"/>
       <c r="F277" s="58"/>
     </row>
     <row r="278" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B278" s="45"/>
       <c r="C278" s="67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D278" s="67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E278" s="58"/>
       <c r="F278" s="58"/>
     </row>
     <row r="279" spans="1:6" ht="160" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B279" s="45"/>
       <c r="C279" s="67" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D279" s="72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E279" s="58"/>
       <c r="F279" s="58"/>
     </row>
     <row r="280" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B280" s="45"/>
       <c r="C280" s="67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D280" s="67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E280" s="58"/>
       <c r="F280" s="58"/>
     </row>
     <row r="281" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C281" s="70" t="s">
         <v>41</v>
@@ -8672,7 +8805,7 @@
     </row>
     <row r="282" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C282" s="70" t="s">
         <v>43</v>
@@ -8685,7 +8818,7 @@
     </row>
     <row r="283" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C283" s="70" t="s">
         <v>45</v>
@@ -8698,7 +8831,7 @@
     </row>
     <row r="284" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C284" s="70" t="s">
         <v>47</v>
@@ -8711,7 +8844,7 @@
     </row>
     <row r="285" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C285" s="70" t="s">
         <v>49</v>
@@ -8724,7 +8857,7 @@
     </row>
     <row r="286" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C286" s="70" t="s">
         <v>51</v>
@@ -8737,7 +8870,7 @@
     </row>
     <row r="287" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C287" s="70" t="s">
         <v>53</v>
@@ -8750,7 +8883,7 @@
     </row>
     <row r="288" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C288" s="70" t="s">
         <v>55</v>
@@ -8763,7 +8896,7 @@
     </row>
     <row r="289" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C289" s="70" t="s">
         <v>57</v>
@@ -8776,7 +8909,7 @@
     </row>
     <row r="290" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C290" s="70" t="s">
         <v>59</v>
@@ -8789,7 +8922,7 @@
     </row>
     <row r="291" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C291" s="70" t="s">
         <v>61</v>
@@ -8802,7 +8935,7 @@
     </row>
     <row r="292" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C292" s="70" t="s">
         <v>63</v>
@@ -8815,7 +8948,7 @@
     </row>
     <row r="293" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C293" s="70" t="s">
         <v>65</v>
@@ -8828,7 +8961,7 @@
     </row>
     <row r="294" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C294" s="70" t="s">
         <v>67</v>
@@ -8841,7 +8974,7 @@
     </row>
     <row r="295" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C295" s="70" t="s">
         <v>69</v>
@@ -8854,7 +8987,7 @@
     </row>
     <row r="296" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C296" s="70" t="s">
         <v>71</v>
@@ -8867,7 +9000,7 @@
     </row>
     <row r="297" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C297" s="70" t="s">
         <v>73</v>
@@ -8880,7 +9013,7 @@
     </row>
     <row r="298" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C298" s="70" t="s">
         <v>75</v>
@@ -8893,7 +9026,7 @@
     </row>
     <row r="299" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C299" s="70" t="s">
         <v>77</v>
@@ -8906,7 +9039,7 @@
     </row>
     <row r="300" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C300" s="70" t="s">
         <v>79</v>
@@ -8919,7 +9052,7 @@
     </row>
     <row r="301" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C301" s="70" t="s">
         <v>81</v>
@@ -8932,7 +9065,7 @@
     </row>
     <row r="302" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C302" s="70" t="s">
         <v>83</v>
@@ -8945,7 +9078,7 @@
     </row>
     <row r="303" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C303" s="70" t="s">
         <v>41</v>
@@ -8958,7 +9091,7 @@
     </row>
     <row r="304" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C304" s="70" t="s">
         <v>43</v>
@@ -8971,7 +9104,7 @@
     </row>
     <row r="305" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C305" s="70" t="s">
         <v>45</v>
@@ -8984,7 +9117,7 @@
     </row>
     <row r="306" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C306" s="70" t="s">
         <v>47</v>
@@ -8997,7 +9130,7 @@
     </row>
     <row r="307" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C307" s="70" t="s">
         <v>49</v>
@@ -9010,7 +9143,7 @@
     </row>
     <row r="308" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C308" s="70" t="s">
         <v>51</v>
@@ -9023,7 +9156,7 @@
     </row>
     <row r="309" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C309" s="70" t="s">
         <v>53</v>
@@ -9036,7 +9169,7 @@
     </row>
     <row r="310" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C310" s="70" t="s">
         <v>55</v>
@@ -9049,7 +9182,7 @@
     </row>
     <row r="311" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C311" s="70" t="s">
         <v>57</v>
@@ -9062,7 +9195,7 @@
     </row>
     <row r="312" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C312" s="70" t="s">
         <v>59</v>
@@ -9075,7 +9208,7 @@
     </row>
     <row r="313" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C313" s="70" t="s">
         <v>61</v>
@@ -9088,7 +9221,7 @@
     </row>
     <row r="314" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C314" s="70" t="s">
         <v>63</v>
@@ -9101,7 +9234,7 @@
     </row>
     <row r="315" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C315" s="70" t="s">
         <v>65</v>
@@ -9114,7 +9247,7 @@
     </row>
     <row r="316" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C316" s="70" t="s">
         <v>67</v>
@@ -9127,7 +9260,7 @@
     </row>
     <row r="317" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C317" s="70" t="s">
         <v>69</v>
@@ -9140,7 +9273,7 @@
     </row>
     <row r="318" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C318" s="70" t="s">
         <v>71</v>
@@ -9153,7 +9286,7 @@
     </row>
     <row r="319" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C319" s="70" t="s">
         <v>73</v>
@@ -9166,7 +9299,7 @@
     </row>
     <row r="320" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C320" s="70" t="s">
         <v>75</v>
@@ -9179,7 +9312,7 @@
     </row>
     <row r="321" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C321" s="70" t="s">
         <v>77</v>
@@ -9192,7 +9325,7 @@
     </row>
     <row r="322" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C322" s="70" t="s">
         <v>79</v>
@@ -9205,7 +9338,7 @@
     </row>
     <row r="323" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C323" s="70" t="s">
         <v>81</v>
@@ -9218,7 +9351,7 @@
     </row>
     <row r="324" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C324" s="70" t="s">
         <v>83</v>
@@ -9231,133 +9364,133 @@
     </row>
     <row r="325" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B325" s="45"/>
       <c r="C325" s="67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D325" s="67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E325" s="58"/>
       <c r="F325" s="58"/>
     </row>
     <row r="326" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B326" s="45"/>
       <c r="C326" s="67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D326" s="67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E326" s="58"/>
       <c r="F326" s="58"/>
     </row>
     <row r="327" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B327" s="45"/>
       <c r="C327" s="67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D327" s="67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E327" s="58"/>
       <c r="F327" s="58"/>
     </row>
     <row r="328" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B328" s="45"/>
       <c r="C328" s="67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D328" s="67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E328" s="58"/>
       <c r="F328" s="58"/>
     </row>
     <row r="329" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B329" s="45"/>
       <c r="C329" s="67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D329" s="67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E329" s="58"/>
       <c r="F329" s="58"/>
     </row>
     <row r="330" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B330" s="45"/>
       <c r="C330" s="67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D330" s="67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E330" s="58"/>
       <c r="F330" s="58"/>
     </row>
     <row r="331" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B331" s="45"/>
       <c r="C331" s="67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D331" s="67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E331" s="58"/>
       <c r="F331" s="58"/>
     </row>
     <row r="332" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B332" s="45"/>
       <c r="C332" s="67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D332" s="67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E332" s="58"/>
       <c r="F332" s="58"/>
     </row>
     <row r="333" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B333" s="45"/>
       <c r="C333" s="67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D333" s="67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E333" s="58"/>
       <c r="F333" s="58"/>
     </row>
     <row r="334" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C334" s="70" t="s">
         <v>41</v>
@@ -9370,7 +9503,7 @@
     </row>
     <row r="335" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C335" s="70" t="s">
         <v>43</v>
@@ -9383,7 +9516,7 @@
     </row>
     <row r="336" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C336" s="70" t="s">
         <v>45</v>
@@ -9396,7 +9529,7 @@
     </row>
     <row r="337" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C337" s="70" t="s">
         <v>47</v>
@@ -9409,7 +9542,7 @@
     </row>
     <row r="338" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C338" s="70" t="s">
         <v>49</v>
@@ -9422,7 +9555,7 @@
     </row>
     <row r="339" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C339" s="70" t="s">
         <v>51</v>
@@ -9435,7 +9568,7 @@
     </row>
     <row r="340" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C340" s="70" t="s">
         <v>53</v>
@@ -9448,7 +9581,7 @@
     </row>
     <row r="341" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C341" s="70" t="s">
         <v>55</v>
@@ -9461,7 +9594,7 @@
     </row>
     <row r="342" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C342" s="70" t="s">
         <v>57</v>
@@ -9474,7 +9607,7 @@
     </row>
     <row r="343" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C343" s="70" t="s">
         <v>59</v>
@@ -9487,7 +9620,7 @@
     </row>
     <row r="344" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C344" s="70" t="s">
         <v>61</v>
@@ -9500,7 +9633,7 @@
     </row>
     <row r="345" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C345" s="70" t="s">
         <v>63</v>
@@ -9513,7 +9646,7 @@
     </row>
     <row r="346" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C346" s="70" t="s">
         <v>65</v>
@@ -9526,7 +9659,7 @@
     </row>
     <row r="347" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C347" s="70" t="s">
         <v>67</v>
@@ -9539,7 +9672,7 @@
     </row>
     <row r="348" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C348" s="70" t="s">
         <v>69</v>
@@ -9552,7 +9685,7 @@
     </row>
     <row r="349" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C349" s="70" t="s">
         <v>71</v>
@@ -9565,7 +9698,7 @@
     </row>
     <row r="350" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C350" s="70" t="s">
         <v>73</v>
@@ -9578,7 +9711,7 @@
     </row>
     <row r="351" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C351" s="70" t="s">
         <v>75</v>
@@ -9591,7 +9724,7 @@
     </row>
     <row r="352" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C352" s="70" t="s">
         <v>77</v>
@@ -9604,7 +9737,7 @@
     </row>
     <row r="353" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C353" s="70" t="s">
         <v>79</v>
@@ -9617,7 +9750,7 @@
     </row>
     <row r="354" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C354" s="70" t="s">
         <v>81</v>
@@ -9630,7 +9763,7 @@
     </row>
     <row r="355" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C355" s="70" t="s">
         <v>83</v>
@@ -9643,91 +9776,91 @@
     </row>
     <row r="356" spans="1:6" ht="144" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B356" s="45"/>
       <c r="C356" s="67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D356" s="67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E356" s="58"/>
       <c r="F356" s="58"/>
     </row>
     <row r="357" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B357" s="45"/>
       <c r="C357" s="67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D357" s="67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E357" s="58"/>
       <c r="F357" s="58"/>
     </row>
     <row r="358" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B358" s="45"/>
       <c r="C358" s="67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D358" s="67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E358" s="58"/>
       <c r="F358" s="58"/>
     </row>
     <row r="359" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B359" s="45"/>
       <c r="C359" s="67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D359" s="67" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E359" s="58"/>
       <c r="F359" s="58"/>
     </row>
     <row r="360" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B360" s="45"/>
       <c r="C360" s="67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D360" s="67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E360" s="58"/>
       <c r="F360" s="58"/>
     </row>
     <row r="361" spans="1:6" ht="128" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B361" s="45"/>
       <c r="C361" s="67" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D361" s="67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E361" s="58"/>
       <c r="F361" s="58"/>
     </row>
     <row r="362" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C362" s="70" t="s">
         <v>41</v>
@@ -9740,7 +9873,7 @@
     </row>
     <row r="363" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C363" s="70" t="s">
         <v>43</v>
@@ -9753,7 +9886,7 @@
     </row>
     <row r="364" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C364" s="70" t="s">
         <v>45</v>
@@ -9766,7 +9899,7 @@
     </row>
     <row r="365" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C365" s="70" t="s">
         <v>47</v>
@@ -9779,7 +9912,7 @@
     </row>
     <row r="366" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C366" s="70" t="s">
         <v>49</v>
@@ -9792,7 +9925,7 @@
     </row>
     <row r="367" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C367" s="70" t="s">
         <v>51</v>
@@ -9805,7 +9938,7 @@
     </row>
     <row r="368" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C368" s="70" t="s">
         <v>53</v>
@@ -9818,7 +9951,7 @@
     </row>
     <row r="369" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C369" s="70" t="s">
         <v>55</v>
@@ -9831,7 +9964,7 @@
     </row>
     <row r="370" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C370" s="70" t="s">
         <v>57</v>
@@ -9844,7 +9977,7 @@
     </row>
     <row r="371" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C371" s="70" t="s">
         <v>59</v>
@@ -9857,7 +9990,7 @@
     </row>
     <row r="372" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C372" s="70" t="s">
         <v>61</v>
@@ -9870,7 +10003,7 @@
     </row>
     <row r="373" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C373" s="70" t="s">
         <v>63</v>
@@ -9883,7 +10016,7 @@
     </row>
     <row r="374" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C374" s="70" t="s">
         <v>65</v>
@@ -9896,7 +10029,7 @@
     </row>
     <row r="375" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C375" s="70" t="s">
         <v>67</v>
@@ -9909,7 +10042,7 @@
     </row>
     <row r="376" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C376" s="70" t="s">
         <v>69</v>
@@ -9922,7 +10055,7 @@
     </row>
     <row r="377" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C377" s="70" t="s">
         <v>71</v>
@@ -9935,7 +10068,7 @@
     </row>
     <row r="378" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C378" s="70" t="s">
         <v>73</v>
@@ -9948,7 +10081,7 @@
     </row>
     <row r="379" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C379" s="70" t="s">
         <v>75</v>
@@ -9961,7 +10094,7 @@
     </row>
     <row r="380" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C380" s="70" t="s">
         <v>77</v>
@@ -9974,7 +10107,7 @@
     </row>
     <row r="381" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C381" s="70" t="s">
         <v>79</v>
@@ -9987,7 +10120,7 @@
     </row>
     <row r="382" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C382" s="70" t="s">
         <v>81</v>
@@ -10000,7 +10133,7 @@
     </row>
     <row r="383" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C383" s="70" t="s">
         <v>83</v>
@@ -10013,7 +10146,7 @@
     </row>
     <row r="384" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B384" s="45"/>
       <c r="C384" s="71" t="s">
@@ -10027,7 +10160,7 @@
     </row>
     <row r="385" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B385" s="45"/>
       <c r="C385" s="71" t="s">
@@ -10041,231 +10174,231 @@
     </row>
     <row r="386" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B386" s="45"/>
       <c r="C386" s="71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D386" s="67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E386" s="58"/>
       <c r="F386" s="58"/>
     </row>
     <row r="387" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B387" s="45"/>
       <c r="C387" s="71" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D387" s="67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E387" s="58"/>
       <c r="F387" s="58"/>
     </row>
     <row r="388" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B388" s="45"/>
       <c r="C388" s="71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D388" s="67" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E388" s="58"/>
       <c r="F388" s="58"/>
     </row>
     <row r="389" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B389" s="45"/>
       <c r="C389" s="71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D389" s="67" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E389" s="58"/>
       <c r="F389" s="58"/>
     </row>
     <row r="390" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B390" s="45"/>
       <c r="C390" s="71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D390" s="67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E390" s="58"/>
       <c r="F390" s="58"/>
     </row>
     <row r="391" spans="1:6" ht="96" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B391" s="45"/>
       <c r="C391" s="71" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D391" s="67" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E391" s="58"/>
       <c r="F391" s="58"/>
     </row>
     <row r="392" spans="1:6" ht="96" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B392" s="45"/>
       <c r="C392" s="71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D392" s="67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E392" s="58"/>
       <c r="F392" s="58"/>
     </row>
     <row r="393" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B393" s="45"/>
       <c r="C393" s="71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D393" s="67" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E393" s="58"/>
       <c r="F393" s="58"/>
     </row>
     <row r="394" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B394" s="45"/>
       <c r="C394" s="71" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D394" s="67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E394" s="58"/>
       <c r="F394" s="58"/>
     </row>
     <row r="395" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B395" s="45"/>
       <c r="C395" s="71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D395" s="67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E395" s="58"/>
       <c r="F395" s="58"/>
     </row>
     <row r="396" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B396" s="45"/>
       <c r="C396" s="71" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D396" s="67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E396" s="58"/>
       <c r="F396" s="58"/>
     </row>
     <row r="397" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B397" s="45"/>
       <c r="C397" s="71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D397" s="67" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E397" s="58"/>
       <c r="F397" s="58"/>
     </row>
     <row r="398" spans="1:6" ht="380" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B398" s="45"/>
       <c r="C398" s="70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D398" s="67" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E398" s="58"/>
       <c r="F398" s="58"/>
     </row>
     <row r="399" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B399" s="45"/>
       <c r="C399" s="71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D399" s="67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E399" s="58"/>
       <c r="F399" s="58"/>
     </row>
     <row r="400" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B400" s="45"/>
       <c r="C400" s="71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D400" s="67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E400" s="58"/>
       <c r="F400" s="58"/>
     </row>
     <row r="401" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B401" s="45"/>
       <c r="C401" s="71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D401" s="67" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E401" s="58"/>
       <c r="F401" s="58"/>
     </row>
     <row r="402" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C402" s="70" t="s">
         <v>41</v>
@@ -10278,7 +10411,7 @@
     </row>
     <row r="403" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C403" s="70" t="s">
         <v>43</v>
@@ -10291,7 +10424,7 @@
     </row>
     <row r="404" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C404" s="70" t="s">
         <v>45</v>
@@ -10304,7 +10437,7 @@
     </row>
     <row r="405" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C405" s="70" t="s">
         <v>47</v>
@@ -10317,7 +10450,7 @@
     </row>
     <row r="406" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C406" s="70" t="s">
         <v>49</v>
@@ -10330,7 +10463,7 @@
     </row>
     <row r="407" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C407" s="70" t="s">
         <v>51</v>
@@ -10343,7 +10476,7 @@
     </row>
     <row r="408" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C408" s="70" t="s">
         <v>53</v>
@@ -10356,7 +10489,7 @@
     </row>
     <row r="409" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C409" s="70" t="s">
         <v>55</v>
@@ -10369,7 +10502,7 @@
     </row>
     <row r="410" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C410" s="70" t="s">
         <v>57</v>
@@ -10382,7 +10515,7 @@
     </row>
     <row r="411" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C411" s="70" t="s">
         <v>59</v>
@@ -10395,7 +10528,7 @@
     </row>
     <row r="412" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C412" s="70" t="s">
         <v>61</v>
@@ -10408,7 +10541,7 @@
     </row>
     <row r="413" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C413" s="70" t="s">
         <v>63</v>
@@ -10421,7 +10554,7 @@
     </row>
     <row r="414" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C414" s="70" t="s">
         <v>65</v>
@@ -10434,7 +10567,7 @@
     </row>
     <row r="415" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C415" s="70" t="s">
         <v>67</v>
@@ -10447,7 +10580,7 @@
     </row>
     <row r="416" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C416" s="70" t="s">
         <v>69</v>
@@ -10460,7 +10593,7 @@
     </row>
     <row r="417" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C417" s="70" t="s">
         <v>71</v>
@@ -10473,7 +10606,7 @@
     </row>
     <row r="418" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C418" s="70" t="s">
         <v>73</v>
@@ -10486,7 +10619,7 @@
     </row>
     <row r="419" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C419" s="70" t="s">
         <v>75</v>
@@ -10499,7 +10632,7 @@
     </row>
     <row r="420" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C420" s="70" t="s">
         <v>77</v>
@@ -10512,7 +10645,7 @@
     </row>
     <row r="421" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C421" s="70" t="s">
         <v>79</v>
@@ -10525,7 +10658,7 @@
     </row>
     <row r="422" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C422" s="70" t="s">
         <v>81</v>
@@ -10538,7 +10671,7 @@
     </row>
     <row r="423" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C423" s="70" t="s">
         <v>83</v>
@@ -10551,301 +10684,301 @@
     </row>
     <row r="424" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B424" s="45"/>
       <c r="C424" s="67" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D424" s="67" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E424" s="58"/>
       <c r="F424" s="58"/>
     </row>
     <row r="425" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B425" s="45"/>
       <c r="C425" s="67" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D425" s="67" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E425" s="58"/>
       <c r="F425" s="58"/>
     </row>
     <row r="426" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B426" s="45"/>
       <c r="C426" s="67" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D426" s="67" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E426" s="58"/>
       <c r="F426" s="58"/>
     </row>
     <row r="427" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B427" s="45"/>
       <c r="C427" s="67" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D427" s="67" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E427" s="58"/>
       <c r="F427" s="58"/>
     </row>
     <row r="428" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B428" s="45"/>
       <c r="C428" s="67" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D428" s="67" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E428" s="58"/>
       <c r="F428" s="58"/>
     </row>
     <row r="429" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B429" s="45"/>
       <c r="C429" s="67" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D429" s="67" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E429" s="58"/>
       <c r="F429" s="58"/>
     </row>
     <row r="430" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B430" s="45"/>
       <c r="C430" s="67" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D430" s="67" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E430" s="58"/>
       <c r="F430" s="58"/>
     </row>
     <row r="431" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B431" s="45"/>
       <c r="C431" s="67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D431" s="67" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E431" s="58"/>
       <c r="F431" s="58"/>
     </row>
     <row r="432" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B432" s="45"/>
       <c r="C432" s="67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D432" s="67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E432" s="58"/>
       <c r="F432" s="58"/>
     </row>
     <row r="433" spans="1:6" ht="96" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B433" s="45"/>
       <c r="C433" s="67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D433" s="67" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E433" s="58"/>
       <c r="F433" s="58"/>
     </row>
     <row r="434" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B434" s="45"/>
       <c r="C434" s="67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D434" s="67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E434" s="58"/>
       <c r="F434" s="58"/>
     </row>
     <row r="435" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B435" s="45"/>
       <c r="C435" s="67" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D435" s="67" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E435" s="58"/>
       <c r="F435" s="58"/>
     </row>
     <row r="436" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B436" s="45"/>
       <c r="C436" s="67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D436" s="67" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E436" s="58"/>
       <c r="F436" s="58"/>
     </row>
     <row r="437" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B437" s="45"/>
       <c r="C437" s="67" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D437" s="67" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E437" s="58"/>
       <c r="F437" s="58"/>
     </row>
     <row r="438" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B438" s="45"/>
       <c r="C438" s="67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D438" s="67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E438" s="58"/>
       <c r="F438" s="58"/>
     </row>
     <row r="439" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B439" s="45"/>
       <c r="C439" s="67" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D439" s="67" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E439" s="58"/>
       <c r="F439" s="58"/>
     </row>
     <row r="440" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B440" s="45"/>
       <c r="C440" s="67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D440" s="67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E440" s="58"/>
       <c r="F440" s="58"/>
     </row>
     <row r="441" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B441" s="45"/>
       <c r="C441" s="67" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D441" s="67" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E441" s="58"/>
       <c r="F441" s="58"/>
     </row>
     <row r="442" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B442" s="45"/>
       <c r="C442" s="67" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D442" s="67" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E442" s="58"/>
       <c r="F442" s="58"/>
     </row>
     <row r="443" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B443" s="45"/>
       <c r="C443" s="67" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D443" s="67" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E443" s="58"/>
       <c r="F443" s="58"/>
     </row>
     <row r="444" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B444" s="45"/>
       <c r="C444" s="67" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D444" s="67" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E444" s="58"/>
       <c r="F444" s="58"/>
     </row>
     <row r="445" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C445" s="70" t="s">
         <v>41</v>
@@ -10858,7 +10991,7 @@
     </row>
     <row r="446" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C446" s="70" t="s">
         <v>43</v>
@@ -10871,7 +11004,7 @@
     </row>
     <row r="447" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C447" s="70" t="s">
         <v>45</v>
@@ -10884,7 +11017,7 @@
     </row>
     <row r="448" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C448" s="70" t="s">
         <v>47</v>
@@ -10897,7 +11030,7 @@
     </row>
     <row r="449" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C449" s="70" t="s">
         <v>49</v>
@@ -10910,7 +11043,7 @@
     </row>
     <row r="450" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C450" s="70" t="s">
         <v>51</v>
@@ -10923,7 +11056,7 @@
     </row>
     <row r="451" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C451" s="70" t="s">
         <v>53</v>
@@ -10936,7 +11069,7 @@
     </row>
     <row r="452" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C452" s="70" t="s">
         <v>55</v>
@@ -10949,7 +11082,7 @@
     </row>
     <row r="453" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C453" s="70" t="s">
         <v>57</v>
@@ -10962,7 +11095,7 @@
     </row>
     <row r="454" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C454" s="70" t="s">
         <v>59</v>
@@ -10975,7 +11108,7 @@
     </row>
     <row r="455" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C455" s="70" t="s">
         <v>61</v>
@@ -10988,7 +11121,7 @@
     </row>
     <row r="456" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C456" s="70" t="s">
         <v>63</v>
@@ -11001,7 +11134,7 @@
     </row>
     <row r="457" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C457" s="70" t="s">
         <v>65</v>
@@ -11014,7 +11147,7 @@
     </row>
     <row r="458" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C458" s="70" t="s">
         <v>67</v>
@@ -11027,7 +11160,7 @@
     </row>
     <row r="459" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C459" s="70" t="s">
         <v>69</v>
@@ -11040,7 +11173,7 @@
     </row>
     <row r="460" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C460" s="70" t="s">
         <v>71</v>
@@ -11053,7 +11186,7 @@
     </row>
     <row r="461" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C461" s="70" t="s">
         <v>73</v>
@@ -11066,20 +11199,20 @@
     </row>
     <row r="462" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C462" s="70" t="s">
         <v>75</v>
       </c>
       <c r="D462" s="67" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E462" s="58"/>
       <c r="F462" s="58"/>
     </row>
     <row r="463" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C463" s="70" t="s">
         <v>77</v>
@@ -11092,7 +11225,7 @@
     </row>
     <row r="464" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C464" s="70" t="s">
         <v>79</v>
@@ -11105,7 +11238,7 @@
     </row>
     <row r="465" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C465" s="70" t="s">
         <v>81</v>
@@ -11118,7 +11251,7 @@
     </row>
     <row r="466" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C466" s="70" t="s">
         <v>83</v>
@@ -11131,189 +11264,189 @@
     </row>
     <row r="467" spans="1:6" ht="114.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B467" s="45"/>
       <c r="C467" s="67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D467" s="67" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E467" s="58"/>
       <c r="F467" s="58"/>
     </row>
     <row r="468" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B468" s="45"/>
       <c r="C468" s="67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D468" s="67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E468" s="58"/>
       <c r="F468" s="58"/>
     </row>
     <row r="469" spans="1:6" ht="107.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B469" s="45"/>
       <c r="C469" s="67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D469" s="67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E469" s="58"/>
       <c r="F469" s="58"/>
     </row>
     <row r="470" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B470" s="45"/>
       <c r="C470" s="67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D470" s="67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E470" s="58"/>
       <c r="F470" s="58"/>
     </row>
     <row r="471" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B471" s="45"/>
       <c r="C471" s="67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D471" s="67" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E471" s="58"/>
       <c r="F471" s="58"/>
     </row>
     <row r="472" spans="1:6" ht="80" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B472" s="45"/>
       <c r="C472" s="67" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D472" s="67" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E472" s="58"/>
       <c r="F472" s="58"/>
     </row>
     <row r="473" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B473" s="45"/>
       <c r="C473" s="67" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D473" s="67" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E473" s="58"/>
       <c r="F473" s="58"/>
     </row>
     <row r="474" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B474" s="45"/>
       <c r="C474" s="67" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D474" s="67" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E474" s="58"/>
       <c r="F474" s="58"/>
     </row>
     <row r="475" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B475" s="45"/>
       <c r="C475" s="67" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D475" s="67" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E475" s="58"/>
       <c r="F475" s="58"/>
     </row>
     <row r="476" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B476" s="45"/>
       <c r="C476" s="67" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D476" s="67" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E476" s="58"/>
       <c r="F476" s="58"/>
     </row>
     <row r="477" spans="1:6" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B477" s="45"/>
       <c r="C477" s="67" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D477" s="67" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E477" s="58"/>
       <c r="F477" s="58"/>
     </row>
     <row r="478" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B478" s="45"/>
       <c r="C478" s="67" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D478" s="67" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E478" s="58"/>
       <c r="F478" s="58"/>
     </row>
     <row r="479" spans="1:6" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B479" s="45"/>
       <c r="C479" s="67" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D479" s="67" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E479" s="58"/>
       <c r="F479" s="58"/>
     </row>
     <row r="480" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C480" s="70" t="s">
         <v>41</v>
@@ -11326,7 +11459,7 @@
     </row>
     <row r="481" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C481" s="70" t="s">
         <v>43</v>
@@ -11339,7 +11472,7 @@
     </row>
     <row r="482" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C482" s="70" t="s">
         <v>45</v>
@@ -11352,7 +11485,7 @@
     </row>
     <row r="483" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C483" s="70" t="s">
         <v>47</v>
@@ -11365,7 +11498,7 @@
     </row>
     <row r="484" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C484" s="70" t="s">
         <v>49</v>
@@ -11378,7 +11511,7 @@
     </row>
     <row r="485" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C485" s="70" t="s">
         <v>51</v>
@@ -11391,7 +11524,7 @@
     </row>
     <row r="486" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C486" s="70" t="s">
         <v>53</v>
@@ -11404,7 +11537,7 @@
     </row>
     <row r="487" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C487" s="70" t="s">
         <v>55</v>
@@ -11417,7 +11550,7 @@
     </row>
     <row r="488" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C488" s="70" t="s">
         <v>57</v>
@@ -11430,7 +11563,7 @@
     </row>
     <row r="489" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C489" s="70" t="s">
         <v>59</v>
@@ -11443,7 +11576,7 @@
     </row>
     <row r="490" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C490" s="70" t="s">
         <v>61</v>
@@ -11456,7 +11589,7 @@
     </row>
     <row r="491" spans="1:6" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C491" s="70" t="s">
         <v>63</v>
@@ -11469,7 +11602,7 @@
     </row>
     <row r="492" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C492" s="70" t="s">
         <v>65</v>
@@ -11482,7 +11615,7 @@
     </row>
     <row r="493" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C493" s="70" t="s">
         <v>67</v>
@@ -11495,7 +11628,7 @@
     </row>
     <row r="494" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C494" s="70" t="s">
         <v>69</v>
@@ -11508,7 +11641,7 @@
     </row>
     <row r="495" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C495" s="70" t="s">
         <v>71</v>
@@ -11521,7 +11654,7 @@
     </row>
     <row r="496" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C496" s="70" t="s">
         <v>73</v>
@@ -11534,7 +11667,7 @@
     </row>
     <row r="497" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C497" s="70" t="s">
         <v>75</v>
@@ -11547,7 +11680,7 @@
     </row>
     <row r="498" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C498" s="70" t="s">
         <v>77</v>
@@ -11560,7 +11693,7 @@
     </row>
     <row r="499" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C499" s="70" t="s">
         <v>79</v>
@@ -11573,7 +11706,7 @@
     </row>
     <row r="500" spans="1:6" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C500" s="70" t="s">
         <v>81</v>
@@ -11586,7 +11719,7 @@
     </row>
     <row r="501" spans="1:6" ht="64" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C501" s="70" t="s">
         <v>83</v>
@@ -11623,13 +11756,12 @@
   <dimension ref="A1:M448"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="45" customWidth="1"/>
-    <col min="2" max="2" width="28.5" style="45" customWidth="1"/>
-    <col min="3" max="3" width="31.5" style="45" customWidth="1"/>
-    <col min="4" max="4" width="27" style="45" customWidth="1"/>
-    <col min="5" max="5" width="33" style="51" customWidth="1"/>
-    <col min="6" max="6" width="34.83203125" style="45" customWidth="1"/>
-    <col min="7" max="7" width="31.5" style="46" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="45" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="45" customWidth="1"/>
+    <col min="3" max="4" width="21.5" style="45" customWidth="1"/>
+    <col min="5" max="5" width="20" style="51" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" style="45" customWidth="1"/>
+    <col min="7" max="7" width="45.83203125" style="46" customWidth="1"/>
     <col min="8" max="9" width="27.5" style="46" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" style="47" customWidth="1"/>
     <col min="11" max="11" width="23.6640625" style="47" customWidth="1"/>
@@ -11638,45 +11770,45 @@
     <col min="14" max="16384" width="8.5" style="45" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="75" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="75" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="65" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C1" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D1" s="73" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F1" s="73" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L1" s="66" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="80" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -11687,284 +11819,440 @@
         <v>23</v>
       </c>
       <c r="C2" s="77" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D2" s="77" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E2" s="77" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I2" s="76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J2" s="78" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K2" s="78" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L2" s="78" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M2" s="79" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D3" s="46"/>
       <c r="E3" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K3" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L3" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M3" s="48" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="46" t="s">
         <v>403</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>404</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>405</v>
-      </c>
-      <c r="J3" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="K3" s="47" t="s">
-        <v>407</v>
-      </c>
-      <c r="L3" s="45" t="s">
-        <v>408</v>
-      </c>
-      <c r="M3" s="48" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="80" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>402</v>
       </c>
       <c r="D4" s="46"/>
       <c r="E4" s="46" t="s">
+        <v>411</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K4" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L4" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M4" s="48" t="s">
         <v>410</v>
       </c>
-      <c r="F4" s="46" t="s">
-        <v>411</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="K4" s="47" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="J5" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="K5" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="L5" s="45" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>414</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>415</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>416</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>417</v>
-      </c>
-      <c r="J5" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="K5" s="47" t="s">
-        <v>407</v>
-      </c>
-      <c r="L5" s="45" t="s">
-        <v>408</v>
-      </c>
       <c r="M5" s="48" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>522</v>
+        <v>196</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J6" s="47" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K6" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="L6" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M6" s="48"/>
+    </row>
+    <row r="7" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>429</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>431</v>
+      </c>
+      <c r="J7" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="L6" s="45" t="s">
+      <c r="K7" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="M6" s="48"/>
-    </row>
-    <row r="7" spans="1:13" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>419</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>424</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>425</v>
-      </c>
-      <c r="F7" s="46" t="s">
+      <c r="L7" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M7" s="48"/>
+    </row>
+    <row r="8" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="45" t="s">
         <v>426</v>
       </c>
-      <c r="G7" s="46" t="s">
-        <v>427</v>
-      </c>
-      <c r="J7" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="K7" s="47" t="s">
+      <c r="B8" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>432</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>433</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>434</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>435</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>436</v>
+      </c>
+      <c r="J8" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="L7" s="45" t="s">
+      <c r="K8" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="M7" s="48"/>
-    </row>
-    <row r="8" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>419</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>428</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>429</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>430</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>431</v>
-      </c>
-      <c r="J8" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="K8" s="47" t="s">
+      <c r="L8" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M8" s="48"/>
+    </row>
+    <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>438</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>439</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>440</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="J9" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="L8" s="45" t="s">
+      <c r="K9" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="M8" s="85"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="M9" s="86"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E10" s="45"/>
-      <c r="G10" s="45"/>
+      <c r="L9" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M9" s="85"/>
+    </row>
+    <row r="10" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="45" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>444</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>445</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>446</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>447</v>
+      </c>
       <c r="H10" s="45"/>
       <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
+      <c r="J10" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L10" s="45" t="s">
+        <v>409</v>
+      </c>
       <c r="M10" s="86"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="M11" s="48"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="M12" s="49"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="M13" s="49"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C14" s="46"/>
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>442</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>449</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>450</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>451</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>452</v>
+      </c>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K11" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L11" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M11" s="86"/>
+    </row>
+    <row r="12" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="45" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>455</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>458</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L12" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M12" s="48"/>
+    </row>
+    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>460</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>462</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>463</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="L13" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M13" s="48"/>
+    </row>
+    <row r="14" spans="1:13" ht="128" x14ac:dyDescent="0.2">
+      <c r="A14" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>465</v>
+      </c>
       <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="M14" s="49"/>
+      <c r="E14" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="K14" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="L14" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="M14" s="49" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="46"/>
@@ -13356,14 +13644,14 @@
       <c r="E448" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M19cYWhgK3jQnaA6Drux+q23DBF5amY7iGz1I9Yv+bjlwQ2vnbnh/BU9FNr0Dm11raTM9xi0z48+nr3y38UpNg==" saltValue="f9ikiMEhvaOx81GERPO+Ig==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sh4tOU+bVBK7KlCPhoKWoKeCv/j6R4ULcLAQNjnKM1Q1p20BATuLt/UMPMnxdjDWiWgSZihGdI+IFUyzcRgbmg==" saltValue="SMVhVFBUE2F+6j15zeY/Bg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A2:M12" xr:uid="{82E872FA-A563-417D-93EE-85A069DCF95A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G7">
-    <sortCondition descending="1" ref="G7"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G8">
+    <sortCondition descending="1" ref="G8"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations xWindow="83" yWindow="666" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select module from list" sqref="A3:A9 A11:A4501" xr:uid="{9430F1B8-F462-4727-A67E-F453CCF9A7B1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select module from list" sqref="A3:A10 A12:A4501" xr:uid="{9430F1B8-F462-4727-A67E-F453CCF9A7B1}">
       <formula1>Modules</formula1>
     </dataValidation>
   </dataValidations>
@@ -13377,19 +13665,19 @@
           <x14:formula1>
             <xm:f>InputValues!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K250:K4500 K3:K9 K11:K248</xm:sqref>
+          <xm:sqref>K250:K4500 K3:K10 K12:K248</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1A13459F-C146-40F0-B118-AE3CAA78B8BC}">
+          <x14:formula1>
+            <xm:f>InputValues!$C$8:$C$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>L3:L10 L12:L4507</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A7321994-2E87-462B-A811-FC7CC4618B2B}">
           <x14:formula1>
             <xm:f>InputValues!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>J3:J5000</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1A13459F-C146-40F0-B118-AE3CAA78B8BC}">
-          <x14:formula1>
-            <xm:f>InputValues!$C$8:$C$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>L3:L9 L11:L4507</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13402,16 +13690,16 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J4966"/>
+  <dimension ref="A1:J4967"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="54" customWidth="1"/>
-    <col min="2" max="2" width="17" style="54" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="54" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="54" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="54" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="54" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" style="54" customWidth="1"/>
     <col min="6" max="6" width="18.5" style="54" customWidth="1"/>
-    <col min="7" max="7" width="11" style="54" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="54" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="54" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="54" customWidth="1"/>
     <col min="10" max="10" width="31.5" style="50" customWidth="1"/>
@@ -13420,66 +13708,66 @@
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="D1" s="81" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="83" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="H2" s="82" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="I2" s="79" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="J2" s="79" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.2">
@@ -13487,13 +13775,13 @@
         <v>46113</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C3" s="47">
         <v>1</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="E3" s="47">
         <v>150</v>
@@ -13501,13 +13789,11 @@
       <c r="F3" s="54"/>
       <c r="G3" s="54"/>
       <c r="H3" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="I3" s="47" t="s">
-        <v>453</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="I3" s="47"/>
       <c r="J3" s="48" t="s">
-        <v>454</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -13515,73 +13801,70 @@
         <v>46113</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C4" s="47">
         <v>1</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="E4" s="47">
         <v>80</v>
       </c>
       <c r="H4" s="53" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="48" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="106">
         <v>46113</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C5" s="47">
         <v>1</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>457</v>
+        <v>492</v>
       </c>
       <c r="E5" s="47">
         <v>10</v>
       </c>
       <c r="H5" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="I5" s="47" t="s">
-        <v>458</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="I5" s="47"/>
       <c r="J5" s="48" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="106">
         <v>46113</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C6" s="47">
         <v>1</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="E6" s="47">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="I6" s="47"/>
+        <v>489</v>
+      </c>
       <c r="J6" s="48" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -13589,184 +13872,333 @@
         <v>46113</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C7" s="47">
         <v>1</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="E7" s="47">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H7" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="I7" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="J7" s="48"/>
-    </row>
-    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="106">
         <v>46113</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C8" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="E8" s="47">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="I8" s="47" t="s">
-        <v>464</v>
-      </c>
-      <c r="J8" s="48"/>
-    </row>
-    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+      <c r="I8" s="47"/>
+      <c r="J8" s="48" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="106">
         <v>46113</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C9" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="E9" s="47">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="H9" s="53" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="I9" s="47"/>
       <c r="J9" s="48" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="47">
+        <v>1</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="E10" s="47">
+        <v>10</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>445</v>
+      </c>
+      <c r="C11" s="45">
+        <v>1</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>446</v>
+      </c>
+      <c r="E11" s="45">
+        <v>40</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="I11" s="47"/>
+      <c r="J11" s="48" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>450</v>
+      </c>
+      <c r="C12" s="45">
+        <v>1</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>451</v>
+      </c>
+      <c r="E12" s="45">
+        <v>40</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="I12" s="47"/>
+      <c r="J12" s="48" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>456</v>
+      </c>
+      <c r="C13" s="45">
+        <v>1</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="E13" s="45">
+        <v>15</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>462</v>
+      </c>
+      <c r="C14" s="45">
+        <v>1</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="E14" s="45">
+        <v>20</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="I14" s="47"/>
+      <c r="J14" s="48" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B15" s="52" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="84"/>
-      <c r="B10" s="52"/>
-      <c r="H10" s="53"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="84"/>
-      <c r="B11" s="52"/>
-      <c r="H11" s="53"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="84"/>
-      <c r="B12" s="52"/>
-      <c r="H12" s="53"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="84"/>
-      <c r="B13" s="52"/>
-      <c r="H13" s="53"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="84"/>
-      <c r="B14" s="52"/>
-      <c r="H14" s="53"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="84"/>
-      <c r="B15" s="52"/>
-      <c r="H15" s="53"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="84"/>
-      <c r="B16" s="52"/>
-      <c r="H16" s="53"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="84"/>
-      <c r="B17" s="52"/>
-      <c r="H17" s="53"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C15" s="45">
+        <v>1</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>501</v>
+      </c>
+      <c r="E15" s="45">
+        <v>0</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="J15" s="107" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>466</v>
+      </c>
+      <c r="C16" s="45">
+        <v>2</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>503</v>
+      </c>
+      <c r="E16" s="45">
+        <v>0</v>
+      </c>
+      <c r="H16" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="J16" s="107" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="106">
+        <v>46113</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>466</v>
+      </c>
+      <c r="C17" s="45">
+        <v>3</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>504</v>
+      </c>
+      <c r="E17" s="45">
+        <v>0</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="J17" s="107" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="84"/>
       <c r="B18" s="52"/>
       <c r="H18" s="53"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="84"/>
       <c r="B19" s="52"/>
       <c r="H19" s="53"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="84"/>
       <c r="B20" s="52"/>
       <c r="H20" s="53"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="84"/>
       <c r="B21" s="52"/>
       <c r="H21" s="53"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="84"/>
       <c r="B22" s="52"/>
       <c r="H22" s="53"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="84"/>
       <c r="B23" s="52"/>
       <c r="H23" s="53"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="84"/>
       <c r="B24" s="52"/>
       <c r="H24" s="53"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="84"/>
       <c r="B25" s="52"/>
       <c r="H25" s="53"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="84"/>
       <c r="B26" s="52"/>
       <c r="H26" s="53"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="84"/>
       <c r="B27" s="52"/>
       <c r="H27" s="53"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="84"/>
       <c r="B28" s="52"/>
       <c r="H28" s="53"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="84"/>
       <c r="B29" s="52"/>
       <c r="H29" s="53"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="84"/>
       <c r="B30" s="52"/>
       <c r="H30" s="53"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="84"/>
       <c r="B31" s="52"/>
       <c r="H31" s="53"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="84"/>
       <c r="B32" s="52"/>
       <c r="H32" s="53"/>
@@ -14942,7 +15374,7 @@
       <c r="H266" s="53"/>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A267" s="62"/>
+      <c r="A267" s="84"/>
       <c r="B267" s="52"/>
       <c r="H267" s="53"/>
     </row>
@@ -38441,15 +38873,20 @@
       <c r="B4966" s="52"/>
       <c r="H4966" s="53"/>
     </row>
+    <row r="4967" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4967" s="62"/>
+      <c r="B4967" s="52"/>
+      <c r="H4967" s="53"/>
+    </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="bunyGELgD96t1fwBZzUOoJrhKDrSBW7qobewLIZR1OAXdqcoLy+fHmp3hwJ6yJWW9ehW4sZyeaZn34WaU/xmGQ==" saltValue="nYDf+aF28NvzM6bIhNZ5tA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A2:J407" xr:uid="{5149E70B-2FAC-45A3-83DD-277AB4249A77}"/>
+  <autoFilter ref="A2:J408" xr:uid="{5149E70B-2FAC-45A3-83DD-277AB4249A77}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H5000" xr:uid="{A66F815E-8762-4CA5-B17F-5097D87BA4A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B7:B5001" xr:uid="{6D07D44D-047C-427E-9398-5A716AF97033}">
+      <formula1>Metric_ID</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H5001" xr:uid="{A66F815E-8762-4CA5-B17F-5097D87BA4A1}">
       <formula1>"Medicaid, CHIP, Both"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B5 B6:B5000" xr:uid="{6D07D44D-047C-427E-9398-5A716AF97033}">
-      <formula1>Metric_ID</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38462,11 +38899,11 @@
   <sheetPr codeName="Sheet6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL32"/>
+  <dimension ref="A1:AL36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.1640625" customWidth="1"/>
     <col min="28" max="28" width="19.6640625" style="24" customWidth="1"/>
     <col min="29" max="38" width="8.5" style="24"/>
@@ -38474,68 +38911,68 @@
   <sheetData>
     <row r="1" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="G1" t="s">
-        <v>469</v>
+        <v>507</v>
       </c>
       <c r="H1" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="AB1" s="29" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="AC1" s="30"/>
     </row>
     <row r="2" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="C2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="AB2" s="30"/>
       <c r="AC2" s="30"/>
     </row>
     <row r="3" spans="1:29" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C3" t="s">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>85</v>
       </c>
       <c r="AB3" s="31" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="AC3" s="32"/>
     </row>
     <row r="4" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="C4" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>109</v>
@@ -38545,259 +38982,299 @@
     </row>
     <row r="5" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G5" s="21" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>164</v>
       </c>
       <c r="AB5" s="33" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="AC5" s="34" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G6" s="21" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>90</v>
       </c>
       <c r="AB6" s="35" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="AC6" s="36" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="G7" s="21" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>175</v>
       </c>
       <c r="AB7" s="35" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="AC7" s="36" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>194</v>
       </c>
       <c r="AB8" s="35" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="AC8" s="36" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>195</v>
+        <v>531</v>
       </c>
       <c r="AB9" s="30" t="s">
-        <v>494</v>
+        <v>532</v>
       </c>
       <c r="AC9" s="30"/>
     </row>
-    <row r="10" spans="1:29" ht="23" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G10" s="21" t="s">
-        <v>495</v>
+        <v>426</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q10" s="28"/>
-      <c r="AB10" s="30" t="s">
-        <v>496</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="AB10" s="30"/>
       <c r="AC10" s="30"/>
     </row>
     <row r="11" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G11" s="21" t="s">
-        <v>497</v>
+        <v>442</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>224</v>
+        <v>534</v>
       </c>
       <c r="AB11" s="30"/>
       <c r="AC11" s="30"/>
     </row>
-    <row r="12" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G12" s="21" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q12" s="28"/>
-      <c r="AB12" s="31" t="s">
-        <v>499</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="AB12" s="30"/>
       <c r="AC12" s="30"/>
     </row>
-    <row r="13" spans="1:29" ht="23" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G13" s="21" t="s">
-        <v>500</v>
+        <v>459</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="AB13" s="30" t="s">
-        <v>501</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
     </row>
-    <row r="14" spans="1:29" ht="23" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G14" s="21" t="s">
-        <v>502</v>
+        <v>537</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="Q14" s="28"/>
       <c r="AB14" s="30" t="s">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="AC14" s="30"/>
     </row>
     <row r="15" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G15" s="21" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB15" s="30" t="s">
-        <v>505</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AB15" s="30"/>
       <c r="AC15" s="30"/>
     </row>
     <row r="16" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G16" s="21" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>312</v>
+        <v>248</v>
       </c>
       <c r="Q16" s="28"/>
-      <c r="AB16" s="30" t="s">
-        <v>507</v>
+      <c r="AB16" s="31" t="s">
+        <v>541</v>
       </c>
       <c r="AC16" s="30"/>
     </row>
     <row r="17" spans="7:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G17" s="21" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>350</v>
+        <v>249</v>
       </c>
       <c r="AB17" s="30" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="AC17" s="30"/>
     </row>
-    <row r="18" spans="7:29" ht="16" x14ac:dyDescent="0.25">
-      <c r="G18" s="22"/>
+    <row r="18" spans="7:29" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>268</v>
+      </c>
       <c r="Q18" s="28"/>
       <c r="AB18" s="30" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="AC18" s="30"/>
     </row>
-    <row r="19" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="G19" s="23"/>
+    <row r="19" spans="7:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>281</v>
+      </c>
       <c r="AB19" s="30" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="AC19" s="30"/>
     </row>
-    <row r="20" spans="7:29" ht="16" x14ac:dyDescent="0.25">
-      <c r="G20" s="22"/>
+    <row r="20" spans="7:29" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>313</v>
+      </c>
       <c r="Q20" s="28"/>
       <c r="AB20" s="30" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="AC20" s="30"/>
     </row>
-    <row r="21" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB21" s="37" t="s">
-        <v>513</v>
+    <row r="21" spans="7:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="AB21" s="30" t="s">
+        <v>551</v>
       </c>
       <c r="AC21" s="30"/>
     </row>
-    <row r="22" spans="7:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="7:29" ht="16" x14ac:dyDescent="0.25">
+      <c r="G22" s="22"/>
+      <c r="Q22" s="28"/>
       <c r="AB22" s="30" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="AC22" s="30"/>
     </row>
     <row r="23" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB23" s="24" t="s">
-        <v>515</v>
+      <c r="G23" s="23"/>
+      <c r="AB23" s="30" t="s">
+        <v>553</v>
       </c>
       <c r="AC23" s="30"/>
     </row>
-    <row r="24" spans="7:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="7:29" ht="16" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="Q24" s="28"/>
+      <c r="AB24" s="30" t="s">
+        <v>554</v>
+      </c>
       <c r="AC24" s="30"/>
     </row>
     <row r="25" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB25" s="31" t="s">
-        <v>516</v>
+      <c r="AB25" s="37" t="s">
+        <v>555</v>
       </c>
       <c r="AC25" s="30"/>
     </row>
     <row r="26" spans="7:29" x14ac:dyDescent="0.2">
       <c r="AB26" s="30" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="AC26" s="30"/>
     </row>
     <row r="27" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB27" s="30"/>
+      <c r="AB27" s="24" t="s">
+        <v>557</v>
+      </c>
       <c r="AC27" s="30"/>
     </row>
     <row r="28" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB28" s="30" t="s">
-        <v>518</v>
-      </c>
       <c r="AC28" s="30"/>
     </row>
     <row r="29" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB29" s="30"/>
+      <c r="AB29" s="31" t="s">
+        <v>558</v>
+      </c>
+      <c r="AC29" s="30"/>
     </row>
     <row r="30" spans="7:29" x14ac:dyDescent="0.2">
       <c r="AB30" s="30" t="s">
-        <v>519</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="AC30" s="30"/>
     </row>
     <row r="31" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB31" s="24" t="s">
-        <v>520</v>
-      </c>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
     </row>
     <row r="32" spans="7:29" x14ac:dyDescent="0.2">
-      <c r="AB32" s="24" t="s">
-        <v>521</v>
+      <c r="AB32" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="AC32" s="30"/>
+    </row>
+    <row r="33" spans="28:28" x14ac:dyDescent="0.2">
+      <c r="AB33" s="30"/>
+    </row>
+    <row r="34" spans="28:28" x14ac:dyDescent="0.2">
+      <c r="AB34" s="30" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="35" spans="28:28" x14ac:dyDescent="0.2">
+      <c r="AB35" s="24" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="36" spans="28:28" x14ac:dyDescent="0.2">
+      <c r="AB36" s="24" t="s">
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -38971,14 +39448,14 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A50E357-A246-4B95-9FF6-3732BC4E008B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="7477c5b0-3556-406f-9be8-f7a10ad0a7f8"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
